--- a/import/Корректировки/4 неделя/22.09.xlsx
+++ b/import/Корректировки/4 неделя/22.09.xlsx
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Web-прогр.</t>
+  </si>
+  <si>
+    <t>вм.6 п.</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1651,7 @@
         <v>32</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
